--- a/Table.xlsx
+++ b/Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msuna\Desktop\NMC_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D842D5EF-46F1-4A23-8E35-7601FBC9D5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D079A2-0671-4ABF-B17E-1F91DD38FB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>Prabhag No. 23</t>
   </si>
   <si>
-    <t>Zone No 8. Lakadganj</t>
-  </si>
-  <si>
     <t>Prabhag No. 24</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>Prabhag No. 12</t>
   </si>
   <si>
-    <t>Zone No 2. Dharmpeth</t>
-  </si>
-  <si>
     <t>Prabhag No. 13</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Prabhag No. 17</t>
   </si>
   <si>
-    <t>Zone No 4. Dhantoli</t>
-  </si>
-  <si>
     <t>Prabhag No. 33</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>Prabhag No. 16</t>
   </si>
   <si>
-    <t>Zone No 1. Laxmi Nagar</t>
-  </si>
-  <si>
     <t>Prabhag No. 36</t>
   </si>
   <si>
@@ -108,9 +96,6 @@
     <t>Prabhag No. 29</t>
   </si>
   <si>
-    <t>Zone No 3. Hanuman Nagar</t>
-  </si>
-  <si>
     <t>Prabhag No. 31</t>
   </si>
   <si>
@@ -123,9 +108,6 @@
     <t>Prabhag No. 28</t>
   </si>
   <si>
-    <t>Zone No 5. Nehru Nagar</t>
-  </si>
-  <si>
     <t>Prabhag No. 30</t>
   </si>
   <si>
@@ -135,15 +117,9 @@
     <t>Prabhag No. 18</t>
   </si>
   <si>
-    <t>Zone No 6. Gandhibag</t>
-  </si>
-  <si>
     <t>Prabhag No. 2</t>
   </si>
   <si>
-    <t>Zone No 9. AashiNagar</t>
-  </si>
-  <si>
     <t>Prabhag No. 22</t>
   </si>
   <si>
@@ -162,9 +138,6 @@
     <t>Prabhag No. 20</t>
   </si>
   <si>
-    <t>Zone No 7. Satranjipura</t>
-  </si>
-  <si>
     <t>Prabhag No. 5</t>
   </si>
   <si>
@@ -175,6 +148,33 @@
   </si>
   <si>
     <t>Prabhag No. 3</t>
+  </si>
+  <si>
+    <t>Zone No. 1 Laxmi Nagar</t>
+  </si>
+  <si>
+    <t>Zone No. 2 Dharmpeth</t>
+  </si>
+  <si>
+    <t>Zone No. 3 Hanuman Nagar</t>
+  </si>
+  <si>
+    <t>Zone No. 4 Dhantoli</t>
+  </si>
+  <si>
+    <t>Zone No. 5 Nehru Nagar</t>
+  </si>
+  <si>
+    <t>Zone No. 6 Gandhibag</t>
+  </si>
+  <si>
+    <t>Zone No. 7 Satranjipura</t>
+  </si>
+  <si>
+    <t>Zone No. 8 Lakadganj</t>
+  </si>
+  <si>
+    <t>Zone No. 9 AashiNagar</t>
   </si>
 </sst>
 </file>
@@ -598,7 +598,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -606,295 +606,295 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Table.xlsx
+++ b/Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msuna\Desktop\NMC_Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msuna\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D079A2-0671-4ABF-B17E-1F91DD38FB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35DE7AD-6ADA-491C-959C-CD4A61A87312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>Prabhag No. 4</t>
-  </si>
-  <si>
     <t>Prabhag No. 23</t>
   </si>
   <si>
@@ -45,9 +42,6 @@
     <t>Prabhag No. 25</t>
   </si>
   <si>
-    <t>Prabhag No. 1</t>
-  </si>
-  <si>
     <t>Zone No.10 Mangalwari</t>
   </si>
   <si>
@@ -117,39 +111,21 @@
     <t>Prabhag No. 18</t>
   </si>
   <si>
-    <t>Prabhag No. 2</t>
-  </si>
-  <si>
     <t>Prabhag No. 22</t>
   </si>
   <si>
     <t>Prabhag No. 19</t>
   </si>
   <si>
-    <t>Prabhag No. 8</t>
-  </si>
-  <si>
-    <t>Prabhag No. 7</t>
-  </si>
-  <si>
     <t>Prabhag No. 26</t>
   </si>
   <si>
     <t>Prabhag No. 20</t>
   </si>
   <si>
-    <t>Prabhag No. 5</t>
-  </si>
-  <si>
     <t>Prabhag No. 21</t>
   </si>
   <si>
-    <t>Prabhag No. 6</t>
-  </si>
-  <si>
-    <t>Prabhag No. 3</t>
-  </si>
-  <si>
     <t>Zone No. 1 Laxmi Nagar</t>
   </si>
   <si>
@@ -175,6 +151,30 @@
   </si>
   <si>
     <t>Zone No. 9 AashiNagar</t>
+  </si>
+  <si>
+    <t>Prabhag No. 04</t>
+  </si>
+  <si>
+    <t>Prabhag No. 01</t>
+  </si>
+  <si>
+    <t>Prabhag No. 02</t>
+  </si>
+  <si>
+    <t>Prabhag No. 08</t>
+  </si>
+  <si>
+    <t>Prabhag No. 07</t>
+  </si>
+  <si>
+    <t>Prabhag No. 05</t>
+  </si>
+  <si>
+    <t>Prabhag No. 06</t>
+  </si>
+  <si>
+    <t>Prabhag No. 03</t>
   </si>
 </sst>
 </file>
@@ -595,306 +595,306 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Table.xlsx
+++ b/Table.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msuna\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35DE7AD-6ADA-491C-959C-CD4A61A87312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67019105-D58C-4812-BDD7-F4F06257F6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -181,7 +192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,25 +206,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -227,14 +226,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF4FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -262,41 +255,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFD7D7D7"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,8 +550,8 @@
   <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -593,307 +562,307 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" t="s">
         <v>41</v>
       </c>
     </row>
